--- a/output/review/local-2026-03-21/potassium_review.xlsx
+++ b/output/review/local-2026-03-21/potassium_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="potassium" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'potassium'!$A$12:$K$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'potassium'!$A$12:$L$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,59 +593,65 @@
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
       <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>LOINC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>SCTID</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>FSN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Complete aggregation</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Quantitative (all numeric)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Quantitative &amp; convertible</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Qualitative (ordinal / nominal / presence)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Semi-quantitative (test strip)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Panel / order code (no Property)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Use case</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -653,32 +660,32 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>79710-0</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>613991010000103</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Mass content of potassium electrolyte in hair at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Potassium [Mass/mass] in Hair</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -696,12 +703,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -710,32 +722,32 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>59733-6</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>599851010000105</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Mass content of potassium electrolyte in tissue at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Potassium [Mass/mass] in Tissue</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -753,12 +765,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -767,32 +784,32 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>11148-4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>489771010000103</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Mass ratio of potassium electrolyte to creatinine in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Potassium/Creatinine [Mass Ratio] in Urine</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -810,12 +827,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -824,32 +846,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>13798-4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>493911010000107</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Mass ratio of potassium electrolyte to creatinine in urine in 24 hours (observable entity)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Potassium/Creatinine [Mass Ratio] in 24 hour Urine</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -867,12 +889,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -881,32 +908,32 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>108797-2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>715401010000106</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Measurement of potassium electrolyte in serum or plasma (observable entity)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Potassium [Measurement] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -924,12 +951,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -938,32 +970,32 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>111266-3</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>731421010000105</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Measurement of potassium electrolyte in stool (observable entity)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Potassium [Measurement] in Stool</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -981,12 +1013,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -995,32 +1032,32 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>111459-4</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>733031010000100</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Measurement of potassium electrolyte in urine (observable entity)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Potassium [Measurement] in Urine</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1038,12 +1075,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -1052,32 +1094,32 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>43222-9</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>553881010000105</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Ratio of potassium electrolyte to creatinine in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Potassium/Creatinine [Ratio] in Urine</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1095,12 +1137,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1109,32 +1156,32 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>56971-5</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>595971010000109</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Ratio of potassium electrolyte to creatinine in urine in 24 hours (observable entity)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Potassium/Creatinine [Ratio] in 24 hour Urine</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1152,12 +1199,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1166,32 +1218,32 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>32550-6</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>528031010000106</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Substance amount of potassium electrolyte in urine (observable entity)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Potassium [Molar amount] in Urine collected for unspecified duration</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1209,12 +1261,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1223,32 +1280,32 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>50902-6</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>567111010000108</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Substance content of potassium electrolyte in hair at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/mass] in Hair</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1266,12 +1323,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1280,32 +1342,32 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>25506-7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>515971010000108</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Substance content of potassium electrolyte in stool at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/mass] in Stool</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1323,12 +1385,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1337,32 +1404,32 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>27441-5</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>520821010000103</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Substance content of potassium electrolyte in stool in 24 hours (observable entity)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/mass] in 24 hour Stool</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1380,12 +1447,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1394,32 +1466,32 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>33949-9</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>530551010000106</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Substance ratio of potassium electrolyte to creatinine in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Potassium/Creatinine [Molar ratio] in Urine</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -1437,12 +1509,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1451,32 +1528,32 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>56143-1</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>594891010000100</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Substance ratio of potassium electrolyte to creatinine in urine in 24 hours (observable entity)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Potassium/Creatinine [Molar ratio] in 24 hour Urine</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1494,12 +1571,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1508,24 +1590,24 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>75940-7</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>216181010000107</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of potassium electrolyte in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Potassium [Mass/volume] in Blood</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1536,9 +1618,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1551,12 +1633,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1565,24 +1652,24 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>82722-0</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>275021010000105</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of potassium electrolyte in erythrocyte at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Potassium [Mass/volume] in Red Blood Cells</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1593,9 +1680,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1608,12 +1695,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1622,24 +1714,24 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>22760-3</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>510211010000101</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of potassium electrolyte in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Potassium [Mass/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1650,9 +1742,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1665,12 +1757,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1679,24 +1776,24 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>9482-1</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>107341010000103</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of potassium electrolyte in water at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Potassium [Mass/volume] in Water</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1707,9 +1804,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1722,12 +1819,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1736,24 +1838,24 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>42569-4</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>741411010000103</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Mass concentration or substance concentration of potassium electrolyte in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Potassium [Mass or Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1764,9 +1866,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1779,12 +1881,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1793,24 +1900,24 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>49788-3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>200351010000102</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in amniotic fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Amniotic fluid</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1821,9 +1928,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -1836,12 +1943,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1850,24 +1962,24 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>32713-0</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>124271010000102</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in arterial blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Arterial blood</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1878,9 +1990,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -1893,12 +2005,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1907,24 +2024,24 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>6298-4</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>195421010000109</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Blood</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1935,9 +2052,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -1950,12 +2067,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1964,24 +2086,24 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>2821-7</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>95481010000104</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in body fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Body fluid</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1992,9 +2114,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2007,12 +2129,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2021,24 +2148,24 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>39790-1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>82121010000102</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in capillary blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Capillary blood</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2049,9 +2176,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2064,12 +2191,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2078,24 +2210,24 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>2819-1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>46331010000107</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in cerebrospinal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Cerebral spinal fluid</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2106,9 +2238,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2121,12 +2253,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2135,24 +2272,24 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>2820-9</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>41901010000106</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in dialysate at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Dialysis fluid</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2163,9 +2300,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2178,12 +2315,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2192,24 +2334,24 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>2824-1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>85271010000102</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in erythrocyte at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Red Blood Cells</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2220,9 +2362,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2235,12 +2377,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2249,24 +2396,24 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>2822-5</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>139301010000103</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in gastric fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Gastric fluid</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2277,9 +2424,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2292,12 +2439,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2306,24 +2458,24 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>17795-6</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>225261010000108</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in hyperal solution at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Hyperal solution</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2334,9 +2486,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2349,12 +2501,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2363,24 +2520,24 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>41656-0</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>253521010000101</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in mixed venous blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Mixed venous blood</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2391,9 +2548,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2406,12 +2563,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2420,24 +2582,24 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>60218-5</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>249661010000106</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in Mother's milk at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Mother's milk</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2448,9 +2610,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2463,12 +2625,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2477,24 +2644,24 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>39785-1</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>270931010000100</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in peritoneal dialysate at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Peritoneal dialysis fluid</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2505,9 +2672,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2520,12 +2687,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2534,24 +2706,24 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>49789-1</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>195601010000104</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in peritoneal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Peritoneal fluid</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2562,9 +2734,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2577,12 +2749,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2591,24 +2768,24 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>77142-8</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>61521010000100</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in plasma or serum or whole blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Serum, Plasma or Blood</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2619,9 +2796,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -2634,12 +2811,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2648,24 +2830,24 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>2825-8</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>180741010000102</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in saliva at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Saliva (oral fluid)</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2676,9 +2858,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2691,12 +2873,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2705,24 +2892,24 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>2823-3</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>254381010000105</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in serum or plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Serum or Plasma</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2733,9 +2920,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -2748,12 +2935,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2762,24 +2954,24 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>93998-3</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>190021010000106</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in serum or plasma at point in time 1H post dose vasopressin (observable entity)</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Serum or Plasma --1 hour post dose vasopressin</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2790,9 +2982,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -2805,12 +2997,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2819,24 +3016,24 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>94007-2</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>89631010000100</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in serum or plasma at point in time 2H post dose vasopressin (observable entity)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Serum or Plasma --2 hours post dose vasopressin</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2847,9 +3044,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -2862,12 +3059,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2876,24 +3078,24 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>12812-4</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>252001010000108</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in serum or plasma at point in time 2nd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Serum or Plasma --2nd specimen</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2904,9 +3106,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2919,12 +3121,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2933,24 +3140,24 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>12813-2</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>243921010000107</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in serum or plasma at point in time 3rd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Serum or Plasma --3rd specimen</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2961,9 +3168,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2976,12 +3183,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -2990,24 +3202,24 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29349-8</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>253591010000104</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in serum or plasma at point in time post-dialysis (observable entity)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Serum or Plasma --post dialysis</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3018,9 +3230,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -3033,12 +3245,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3047,24 +3264,24 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>51618-7</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>136441010000101</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in serum or plasma at point in time Pre-dialysis (observable entity)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Serum or Plasma --pre dialysis</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3075,9 +3292,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3090,12 +3307,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3104,24 +3326,24 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>32336-0</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>75971010000104</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in specimen at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Specimen</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3132,9 +3354,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3147,12 +3369,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3161,24 +3388,24 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>15202-5</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>247851010000101</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in stool at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Stool</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3189,9 +3416,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3204,12 +3431,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3218,24 +3450,24 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>59162-8</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>140741010000107</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in stool in 24 hours (observable entity)</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in 24 hour Stool</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3246,9 +3478,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3261,12 +3493,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3275,24 +3512,24 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>2827-4</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>258661010000102</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in sweat at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Sweat</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3303,9 +3540,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3318,12 +3555,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3332,24 +3574,24 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>14172-1</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>123581010000104</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in synovial fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Synovial fluid</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3360,9 +3602,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3375,12 +3617,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3389,24 +3636,24 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>30549-0</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>240771010000103</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in TPN at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Total parental nutrition</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3417,9 +3664,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3432,12 +3679,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3446,24 +3698,24 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>35677-4</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>201301010000105</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in urine (observable entity)</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Urine collected for unspecified duration</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3474,9 +3726,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3489,12 +3741,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3503,24 +3760,24 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>2828-2</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>179881010000103</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Urine</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3531,9 +3788,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3546,12 +3803,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3560,24 +3822,24 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>57355-0</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>150811010000104</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in urine in 12 hours (observable entity)</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in 12 hour Urine</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3588,9 +3850,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3603,12 +3865,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3617,24 +3884,24 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>57379-0</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>189611010000103</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in urine in 2 hours (observable entity)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in 2 hour Urine</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3645,9 +3912,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -3660,12 +3927,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3674,24 +3946,24 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>21476-7</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>195291010000107</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in urine in 24 hours (observable entity)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in 24 hour Urine</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3702,9 +3974,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3717,12 +3989,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3731,24 +4008,24 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>94841-4</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>117691010000102</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in Urine^Fetus at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Urine from Fetus</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3759,9 +4036,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3774,12 +4051,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3788,24 +4070,24 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>39789-3</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>203891010000109</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in venous blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Venous blood</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3816,9 +4098,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3831,12 +4113,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3845,24 +4132,24 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>12814-0</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>139701010000102</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of potassium electrolyte in vitreous humor at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Potassium [Moles/volume] in Vitreous fluid</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3873,9 +4160,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3888,19 +4175,24 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:K70"/>
+  <autoFilter ref="A12:L70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>